--- a/grupos/3AEV - Estadisticos 20231.xlsx
+++ b/grupos/3AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -2725,13 +2725,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2740,22 +2740,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2766,51 +2769,60 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -2821,87 +2833,96 @@
         <v>95</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
         <v>85</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
       <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
         <v>95</v>
       </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
         <v>85</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
-      <c r="M4">
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
         <v>95</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
       <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5">
         <v>80</v>
       </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
       <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
         <v>96.7</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>85</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>80</v>
       </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
-      <c r="J5">
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>96.7</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>85</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>80</v>
       </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
-      <c r="O5">
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>96.7</v>
       </c>
-      <c r="P5">
+      <c r="S5">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2912,46 +2933,55 @@
         <v>90</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
         <v>95</v>
       </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
       <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
         <v>90</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
         <v>95</v>
       </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
-      <c r="M6">
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
         <v>90</v>
       </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -2962,46 +2992,55 @@
         <v>85</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
         <v>96.7</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>80</v>
       </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
       <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
         <v>85</v>
       </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>96.7</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>80</v>
       </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
         <v>85</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>96.7</v>
       </c>
-      <c r="P7">
+      <c r="S7">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3012,46 +3051,55 @@
         <v>90</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
         <v>96.7</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>85</v>
       </c>
-      <c r="G8">
-        <v>100</v>
-      </c>
       <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
         <v>90</v>
       </c>
-      <c r="I8">
-        <v>100</v>
-      </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>96.7</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>85</v>
       </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
-      <c r="M8">
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>90</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>96.7</v>
       </c>
-      <c r="P8">
+      <c r="S8">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3062,46 +3110,55 @@
         <v>80</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
         <v>96.7</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>65</v>
       </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
       <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
         <v>80</v>
       </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
         <v>96.7</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>65</v>
       </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
-      <c r="M9">
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>80</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>96.7</v>
       </c>
-      <c r="P9">
+      <c r="S9">
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3112,17 +3169,17 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
         <v>96.7</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>85</v>
       </c>
-      <c r="G10">
-        <v>100</v>
-      </c>
       <c r="H10">
         <v>100</v>
       </c>
@@ -3130,28 +3187,37 @@
         <v>100</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>96.7</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>85</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
       <c r="N10">
         <v>100</v>
       </c>
       <c r="O10">
+        <v>100</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>96.7</v>
       </c>
-      <c r="P10">
+      <c r="S10">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3162,17 +3228,17 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
         <v>96.7</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>85</v>
       </c>
-      <c r="G11">
-        <v>100</v>
-      </c>
       <c r="H11">
         <v>100</v>
       </c>
@@ -3180,28 +3246,37 @@
         <v>100</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>96.7</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>85</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>96.7</v>
       </c>
-      <c r="P11">
+      <c r="S11">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3212,28 +3287,28 @@
         <v>95</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>100</v>
       </c>
       <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
         <v>95</v>
       </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
       <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
         <v>95</v>
       </c>
-      <c r="I12">
-        <v>100</v>
-      </c>
       <c r="J12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -3245,13 +3320,22 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3262,46 +3346,55 @@
         <v>90</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E13">
+        <v>100</v>
+      </c>
+      <c r="F13">
         <v>96.7</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>80</v>
       </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
       <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
         <v>90</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>96.7</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>80</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>90</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>96.7</v>
       </c>
-      <c r="P13">
+      <c r="S13">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3312,46 +3405,55 @@
         <v>85</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
         <v>80</v>
       </c>
-      <c r="G14">
-        <v>100</v>
-      </c>
       <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
         <v>85</v>
       </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
       <c r="J14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14">
         <v>80</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
+      <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>85</v>
       </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
       <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -3362,17 +3464,17 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>100</v>
       </c>
       <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15">
         <v>85</v>
       </c>
-      <c r="G15">
-        <v>100</v>
-      </c>
       <c r="H15">
         <v>100</v>
       </c>
@@ -3380,17 +3482,17 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
         <v>85</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
       <c r="N15">
         <v>100</v>
       </c>
@@ -3398,10 +3500,19 @@
         <v>100</v>
       </c>
       <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -3412,69 +3523,78 @@
         <v>90</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16">
+        <v>100</v>
+      </c>
+      <c r="F16">
         <v>96.7</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>80</v>
       </c>
-      <c r="G16">
-        <v>100</v>
-      </c>
       <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
         <v>90</v>
       </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
         <v>96.7</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>80</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
-      <c r="M16">
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
         <v>90</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>96.7</v>
       </c>
-      <c r="P16">
+      <c r="S16">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
       <c r="E17">
+        <v>100</v>
+      </c>
+      <c r="F17">
         <v>96.7</v>
       </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
-      <c r="J17">
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>96.7</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
         <v>96.7</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -3485,17 +3605,17 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>100</v>
       </c>
       <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
         <v>70</v>
       </c>
-      <c r="G18">
-        <v>100</v>
-      </c>
       <c r="H18">
         <v>100</v>
       </c>
@@ -3503,17 +3623,17 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>70</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
         <v>100</v>
       </c>
@@ -3521,10 +3641,19 @@
         <v>100</v>
       </c>
       <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -3535,46 +3664,55 @@
         <v>95</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E19">
+        <v>100</v>
+      </c>
+      <c r="F19">
         <v>96.7</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>85</v>
       </c>
-      <c r="G19">
-        <v>100</v>
-      </c>
       <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
         <v>95</v>
       </c>
-      <c r="I19">
-        <v>100</v>
-      </c>
       <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>96.7</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>85</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
+      <c r="N19">
+        <v>100</v>
+      </c>
+      <c r="O19">
         <v>95</v>
       </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
-      <c r="O19">
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>96.7</v>
       </c>
-      <c r="P19">
+      <c r="S19">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -3585,31 +3723,31 @@
         <v>95</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20">
+        <v>100</v>
+      </c>
+      <c r="F20">
         <v>96.7</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>95</v>
       </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
       <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
         <v>95</v>
       </c>
-      <c r="I20">
-        <v>100</v>
-      </c>
       <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>96.7</v>
-      </c>
-      <c r="K20">
-        <v>95</v>
-      </c>
-      <c r="L20">
-        <v>100</v>
       </c>
       <c r="M20">
         <v>95</v>
@@ -3618,13 +3756,22 @@
         <v>100</v>
       </c>
       <c r="O20">
+        <v>95</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>96.7</v>
       </c>
-      <c r="P20">
+      <c r="S20">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -3635,7 +3782,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -3653,7 +3800,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -3671,10 +3818,19 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -3685,17 +3841,17 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22">
+        <v>100</v>
+      </c>
+      <c r="F22">
         <v>96.7</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>95</v>
       </c>
-      <c r="G22">
-        <v>100</v>
-      </c>
       <c r="H22">
         <v>100</v>
       </c>
@@ -3703,28 +3859,37 @@
         <v>100</v>
       </c>
       <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>96.7</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>95</v>
       </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>96.7</v>
       </c>
-      <c r="P22">
+      <c r="S22">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -3735,46 +3900,55 @@
         <v>85</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
         <v>96.7</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>90</v>
       </c>
-      <c r="G23">
-        <v>100</v>
-      </c>
       <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
         <v>85</v>
       </c>
-      <c r="I23">
-        <v>100</v>
-      </c>
       <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
         <v>96.7</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>90</v>
       </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
-      <c r="M23">
+      <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
         <v>85</v>
       </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23">
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>96.7</v>
       </c>
-      <c r="P23">
+      <c r="S23">
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -3785,46 +3959,55 @@
         <v>95</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
         <v>96.7</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>90</v>
       </c>
-      <c r="G24">
-        <v>100</v>
-      </c>
       <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
         <v>95</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
       <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
         <v>96.7</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>90</v>
       </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
-      <c r="M24">
+      <c r="N24">
+        <v>100</v>
+      </c>
+      <c r="O24">
         <v>95</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>96.7</v>
       </c>
-      <c r="P24">
+      <c r="S24">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -3835,7 +4018,7 @@
         <v>95</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -3847,13 +4030,13 @@
         <v>100</v>
       </c>
       <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
         <v>95</v>
       </c>
-      <c r="I25">
-        <v>100</v>
-      </c>
       <c r="J25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -3862,19 +4045,28 @@
         <v>100</v>
       </c>
       <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
+        <v>100</v>
+      </c>
+      <c r="O25">
         <v>95</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
       <c r="P25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -3885,46 +4077,55 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
         <v>96.7</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>70</v>
       </c>
-      <c r="G26">
-        <v>100</v>
-      </c>
       <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
         <v>65</v>
       </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>96.7</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>70</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="M26">
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>65</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>96.7</v>
       </c>
-      <c r="P26">
+      <c r="S26">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -3935,46 +4136,55 @@
         <v>90</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27">
         <v>96.7</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>85</v>
       </c>
-      <c r="G27">
-        <v>100</v>
-      </c>
       <c r="H27">
+        <v>100</v>
+      </c>
+      <c r="I27">
         <v>90</v>
       </c>
-      <c r="I27">
-        <v>100</v>
-      </c>
       <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
         <v>96.7</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>85</v>
       </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
-      <c r="M27">
+      <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
         <v>90</v>
       </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
-      <c r="O27">
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>96.7</v>
       </c>
-      <c r="P27">
+      <c r="S27">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -3985,17 +4195,17 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E28">
+        <v>100</v>
+      </c>
+      <c r="F28">
         <v>96.7</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>90</v>
       </c>
-      <c r="G28">
-        <v>100</v>
-      </c>
       <c r="H28">
         <v>100</v>
       </c>
@@ -4003,32 +4213,41 @@
         <v>100</v>
       </c>
       <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>96.7</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>90</v>
       </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
       <c r="N28">
         <v>100</v>
       </c>
       <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>96.7</v>
       </c>
-      <c r="P28">
+      <c r="S28">
         <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3AEV - Estadisticos 20231.xlsx
+++ b/grupos/3AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -107,7 +107,7 @@
     <t>MOLINA DE JESUS VICTOR MANUEL</t>
   </si>
   <si>
-    <t>PUGA CABRERA  ELIAS</t>
+    <t>PUGA CABRERA ELIAS</t>
   </si>
   <si>
     <t>ROSAS SERRANO CRISTOPHER</t>
@@ -167,15 +167,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -194,19 +194,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>COBOS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -215,15 +209,9 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LOBATO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MARQUEZ</t>
   </si>
   <si>
@@ -233,82 +221,58 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>TIZA</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>YOLET</t>
   </si>
   <si>
     <t>DAVID</t>
@@ -317,15 +281,9 @@
     <t>PATRICIO</t>
   </si>
   <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
     <t>FABIAN ALEJANDRO</t>
   </si>
   <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
     <t>CRISTIAN OSMAR</t>
   </si>
   <si>
@@ -335,46 +293,16 @@
     <t>VICTOR MANUEL</t>
   </si>
   <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
     <t>JOSUE GUSTAVO</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
     <t>OSMAR</t>
   </si>
   <si>
     <t>NAHUM HIRAM</t>
   </si>
   <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
     <t>ERIK</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
   </si>
 </sst>
 </file>
@@ -870,7 +798,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -882,22 +810,22 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -918,22 +846,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -953,16 +881,16 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -986,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1000,7 +928,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>9</v>
@@ -1012,22 +940,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1048,13 +976,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1077,7 +1005,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1089,22 +1017,22 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1125,22 +1053,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1154,7 +1082,7 @@
         <v>5</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1166,22 +1094,22 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1202,16 +1130,16 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1231,7 +1159,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1243,22 +1171,22 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1279,19 +1207,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1308,7 +1236,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1320,22 +1248,22 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1359,19 +1287,19 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1385,7 +1313,7 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -1397,22 +1325,22 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1436,19 +1364,19 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1462,7 +1390,7 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1474,22 +1402,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1510,22 +1438,22 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1539,7 +1467,7 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -1551,22 +1479,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1593,16 +1521,16 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1616,7 +1544,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1628,22 +1556,22 @@
         <v>4</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1664,13 +1592,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1693,7 +1621,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>8</v>
@@ -1705,22 +1633,22 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1744,19 +1672,19 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1770,7 +1698,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -1782,22 +1710,22 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1821,16 +1749,16 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1847,10 +1775,10 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1876,7 +1804,7 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -1888,22 +1816,22 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1924,19 +1852,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1953,7 +1881,7 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -1965,22 +1893,22 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2004,19 +1932,19 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2030,7 +1958,7 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>7</v>
@@ -2042,22 +1970,22 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2078,19 +2006,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2107,7 +2035,7 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>9</v>
@@ -2119,22 +2047,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2155,19 +2083,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2184,7 +2112,7 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2196,22 +2124,22 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2232,19 +2160,19 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2261,7 +2189,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>9</v>
@@ -2273,22 +2201,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2309,22 +2237,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2338,7 +2266,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>8</v>
@@ -2350,22 +2278,22 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2386,22 +2314,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>8</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2415,7 +2343,7 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2427,22 +2355,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2469,10 +2397,10 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2492,7 +2420,7 @@
         <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -2504,22 +2432,22 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2546,16 +2474,16 @@
         <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2569,7 +2497,7 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -2581,22 +2509,22 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2617,13 +2545,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2632,7 +2560,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2646,7 +2574,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>8</v>
@@ -2658,22 +2586,22 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2694,22 +2622,22 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2833,7 +2761,7 @@
         <v>95</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -2848,10 +2776,10 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -2860,16 +2788,16 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -2878,7 +2806,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2898,25 +2826,25 @@
         <v>85</v>
       </c>
       <c r="I5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M5">
         <v>85</v>
       </c>
       <c r="O5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S5">
         <v>85</v>
@@ -2933,7 +2861,7 @@
         <v>90</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -2948,10 +2876,10 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -2966,10 +2894,10 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -2992,7 +2920,7 @@
         <v>85</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3007,37 +2935,37 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S7">
-        <v>80</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3051,7 +2979,7 @@
         <v>90</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3066,37 +2994,37 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>95</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
+        <v>98.5</v>
+      </c>
+      <c r="M8">
         <v>90</v>
       </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
-      <c r="L8">
-        <v>96.7</v>
-      </c>
-      <c r="M8">
-        <v>85</v>
-      </c>
       <c r="N8">
         <v>100</v>
       </c>
       <c r="O8">
+        <v>95</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
+        <v>98.5</v>
+      </c>
+      <c r="S8">
         <v>90</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
-        <v>96.7</v>
-      </c>
-      <c r="S8">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3110,7 +3038,7 @@
         <v>80</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -3125,37 +3053,37 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M9">
-        <v>65</v>
+        <v>77.5</v>
       </c>
       <c r="N9">
         <v>100</v>
       </c>
       <c r="O9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S9">
-        <v>65</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3169,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -3187,16 +3115,16 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M10">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -3205,16 +3133,16 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S10">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3228,7 +3156,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -3246,16 +3174,16 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M11">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3264,16 +3192,16 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S11">
-        <v>85</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3287,7 +3215,7 @@
         <v>95</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -3302,10 +3230,10 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3314,16 +3242,16 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3332,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3346,7 +3274,7 @@
         <v>90</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -3364,13 +3292,13 @@
         <v>90</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M13">
         <v>80</v>
@@ -3382,13 +3310,13 @@
         <v>90</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S13">
         <v>80</v>
@@ -3405,7 +3333,7 @@
         <v>85</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -3420,10 +3348,10 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -3432,16 +3360,16 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3450,7 +3378,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3464,7 +3392,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -3482,7 +3410,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -3491,7 +3419,7 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -3500,7 +3428,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3509,7 +3437,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>85</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3523,7 +3451,7 @@
         <v>90</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -3538,37 +3466,37 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M16">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S16">
-        <v>80</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3582,16 +3510,16 @@
         <v>96.7</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L17">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R17">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3605,7 +3533,7 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -3623,7 +3551,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -3632,7 +3560,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -3641,7 +3569,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3650,7 +3578,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>70</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3664,7 +3592,7 @@
         <v>95</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -3679,37 +3607,37 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M19">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S19">
-        <v>85</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3723,7 +3651,7 @@
         <v>95</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -3738,37 +3666,37 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M20">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="N20">
         <v>100</v>
       </c>
       <c r="O20">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S20">
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3782,7 +3710,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -3800,7 +3728,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -3809,7 +3737,7 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -3818,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -3827,7 +3755,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3841,7 +3769,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -3859,16 +3787,16 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -3877,16 +3805,16 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3900,7 +3828,7 @@
         <v>85</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -3915,16 +3843,16 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M23">
         <v>90</v>
@@ -3933,16 +3861,16 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S23">
         <v>90</v>
@@ -3959,7 +3887,7 @@
         <v>95</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -3974,37 +3902,37 @@
         <v>100</v>
       </c>
       <c r="I24">
+        <v>97.5</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
+        <v>98.5</v>
+      </c>
+      <c r="M24">
         <v>95</v>
       </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
-      <c r="L24">
-        <v>96.7</v>
-      </c>
-      <c r="M24">
-        <v>90</v>
-      </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
+        <v>97.5</v>
+      </c>
+      <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>98.5</v>
+      </c>
+      <c r="S24">
         <v>95</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>96.7</v>
-      </c>
-      <c r="S24">
-        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4018,7 +3946,7 @@
         <v>95</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -4033,10 +3961,10 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4051,10 +3979,10 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4077,7 +4005,7 @@
         <v>65</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4092,37 +4020,37 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M26">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S26">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4136,7 +4064,7 @@
         <v>90</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -4151,37 +4079,37 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M27">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="N27">
         <v>100</v>
       </c>
       <c r="O27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S27">
-        <v>85</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4195,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -4213,16 +4141,16 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="M28">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4231,16 +4159,16 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="S28">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4297,36 +4225,39 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2">
+        <v>50</v>
+      </c>
+      <c r="G2" s="2">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>23</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4335,19 +4266,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>54.2</v>
+        <v>79.2</v>
       </c>
       <c r="G3" s="2">
-        <v>45.8</v>
+        <v>20.8</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4358,28 +4289,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>87</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>13</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4399,19 +4330,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="G5" s="2">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4422,7 +4353,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
@@ -4431,19 +4362,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4454,7 +4385,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -4475,7 +4406,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4491,7 +4422,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4518,463 +4449,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920177</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920179</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920389</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920183</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920184</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920185</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920188</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920197</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920190</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920413</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920378</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920359</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920192</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920193</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920197</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920358</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920356</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920180</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920363</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920200</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920371</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920201</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920202</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4982,7 +4456,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5014,22 +4488,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920007</v>
+        <v>22330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5037,22 +4511,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920007</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5060,22 +4534,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920184</v>
+        <v>19330051920067</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5083,45 +4557,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920184</v>
+        <v>19330051920067</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920188</v>
+        <v>22330051920378</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5129,45 +4603,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920188</v>
+        <v>22330051920378</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
         <v>83</v>
       </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920067</v>
+        <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5175,22 +4649,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920067</v>
+        <v>22330051920188</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5198,22 +4672,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920180</v>
+        <v>21330051920197</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5221,42 +4695,42 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920180</v>
+        <v>22330051920413</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920200</v>
+        <v>22330051920359</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>50</v>
@@ -5267,298 +4741,140 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920200</v>
+        <v>22330051920192</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>49</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920177</v>
+        <v>22330051920193</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>49</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920179</v>
+        <v>22330051920356</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920183</v>
+        <v>22330051920363</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920185</v>
+        <v>22330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>49</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920413</v>
+        <v>22330051920202</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>49</v>
       </c>
       <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920193</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920197</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920358</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920356</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920363</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920201</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920202</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3AEV - Estadisticos 20231.xlsx
+++ b/grupos/3AEV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -167,12 +167,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -194,115 +194,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
   </si>
   <si>
     <t>ARACELY</t>
   </si>
   <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
     <t>OSMAR</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -828,28 +762,28 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -858,7 +792,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -893,19 +827,19 @@
         <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -958,25 +892,25 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -988,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1035,34 +969,34 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1112,22 +1046,22 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1142,7 +1076,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1189,19 +1123,19 @@
         <v>3</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1210,10 +1144,10 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1266,25 +1200,25 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1299,7 +1233,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1343,28 +1277,28 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1420,28 +1354,28 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1497,31 +1431,31 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1530,7 +1464,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1574,28 +1508,28 @@
         <v>3</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1651,31 +1585,31 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1684,7 +1618,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1728,40 +1662,40 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>8</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1781,16 +1715,16 @@
         <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1834,22 +1768,22 @@
         <v>3</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1858,13 +1792,13 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1896,7 +1830,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -1911,40 +1845,40 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1988,31 +1922,31 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>8</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2021,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2065,31 +1999,31 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2142,31 +2076,31 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2219,40 +2153,40 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2296,28 +2230,28 @@
         <v>3</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2373,37 +2307,37 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>7</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2450,31 +2384,31 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2527,37 +2461,37 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>8</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2604,31 +2538,31 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -2794,10 +2728,10 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -2806,7 +2740,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>90</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2838,16 +2772,16 @@
         <v>85</v>
       </c>
       <c r="O5">
-        <v>85</v>
+        <v>90.3</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S5">
-        <v>85</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2894,10 +2828,10 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -2906,7 +2840,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>95</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2953,19 +2887,19 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S7">
-        <v>87.5</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3012,19 +2946,19 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S8">
-        <v>90</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3071,19 +3005,19 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>85</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S9">
-        <v>77.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3139,10 +3073,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3192,16 +3126,16 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S11">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3248,10 +3182,10 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3260,7 +3194,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>97.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3307,19 +3241,19 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S13">
-        <v>80</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3366,7 +3300,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3378,7 +3312,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>90</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3425,10 +3359,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3437,7 +3371,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>87.5</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3484,19 +3418,19 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S16">
-        <v>87.5</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3516,10 +3450,10 @@
         <v>98.5</v>
       </c>
       <c r="Q17">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="R17">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3569,7 +3503,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3578,7 +3512,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>72.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3625,19 +3559,19 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S19">
-        <v>87.5</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3684,19 +3618,19 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S20">
-        <v>92.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3746,7 +3680,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -3755,7 +3689,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>92.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3805,16 +3739,16 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S22">
-        <v>97.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3861,19 +3795,19 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S23">
-        <v>90</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3920,19 +3854,19 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S24">
-        <v>95</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3979,10 +3913,10 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4038,7 +3972,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>82.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4047,10 +3981,10 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S26">
-        <v>85</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4097,19 +4031,19 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S27">
-        <v>92.5</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4159,16 +4093,16 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="S28">
-        <v>95</v>
+        <v>96.8</v>
       </c>
     </row>
   </sheetData>
@@ -4225,7 +4159,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4234,19 +4168,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>50</v>
+        <v>79.2</v>
       </c>
       <c r="G2" s="2">
-        <v>50</v>
+        <v>20.8</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4257,7 +4191,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4266,19 +4200,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>79.2</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4298,19 +4232,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4330,19 +4264,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4362,19 +4296,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4394,19 +4328,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4456,7 +4390,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4488,19 +4422,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920190</v>
+        <v>22330051920389</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
@@ -4511,22 +4445,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920190</v>
+        <v>22330051920188</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4534,22 +4468,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920067</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4557,22 +4491,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920067</v>
+        <v>22330051920378</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4580,300 +4514,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920378</v>
+        <v>22330051920363</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920378</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920188</v>
-      </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920197</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920413</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920359</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920192</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920193</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920356</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920363</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920200</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920202</v>
-      </c>
-      <c r="B18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEV - Estadisticos 20231.xlsx
+++ b/grupos/3AEV - Estadisticos 20231.xlsx
@@ -1138,7 +1138,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1523,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -2399,7 +2399,7 @@
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2417,7 +2417,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -3017,7 +3017,7 @@
         <v>99</v>
       </c>
       <c r="S9">
-        <v>49.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3312,7 +3312,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>57.1</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3984,7 +3984,7 @@
         <v>99</v>
       </c>
       <c r="S26">
-        <v>54</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">

--- a/grupos/3AEV - Estadisticos 20231.xlsx
+++ b/grupos/3AEV - Estadisticos 20231.xlsx
@@ -780,22 +780,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -839,16 +839,16 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -910,22 +910,22 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -987,22 +987,22 @@
         <v>6</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1064,22 +1064,22 @@
         <v>7</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1141,19 +1141,19 @@
         <v>8</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1218,22 +1218,22 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1295,22 +1295,22 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1372,19 +1372,19 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1449,19 +1449,19 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1526,19 +1526,19 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1603,22 +1603,22 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1680,22 +1680,22 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1721,10 +1721,10 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1786,19 +1786,19 @@
         <v>3</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1863,22 +1863,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1940,22 +1940,22 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2017,22 +2017,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2094,22 +2094,22 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2171,22 +2171,22 @@
         <v>6</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2248,19 +2248,19 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2325,22 +2325,22 @@
         <v>7</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2402,22 +2402,22 @@
         <v>5</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2479,22 +2479,22 @@
         <v>6</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2556,22 +2556,22 @@
         <v>7</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4180,7 +4180,7 @@
         <v>20.8</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4212,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3AEV - Estadisticos 20231.xlsx
+++ b/grupos/3AEV - Estadisticos 20231.xlsx
@@ -780,22 +780,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -839,16 +839,16 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -910,22 +910,22 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -987,22 +987,22 @@
         <v>6</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1064,22 +1064,22 @@
         <v>7</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1141,19 +1141,19 @@
         <v>8</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1218,22 +1218,22 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1295,22 +1295,22 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1372,19 +1372,19 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1449,19 +1449,19 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1526,19 +1526,19 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1603,22 +1603,22 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1680,22 +1680,22 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1721,10 +1721,10 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1786,19 +1786,19 @@
         <v>3</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1863,22 +1863,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1940,22 +1940,22 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2017,22 +2017,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2094,22 +2094,22 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2171,22 +2171,22 @@
         <v>6</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2248,19 +2248,19 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2325,22 +2325,22 @@
         <v>7</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2402,22 +2402,22 @@
         <v>5</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2479,22 +2479,22 @@
         <v>6</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2556,22 +2556,22 @@
         <v>7</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4180,7 +4180,7 @@
         <v>20.8</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4212,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
